--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R82415358312d4bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rb551c0395661431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R28ff924783df42e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R887ca6a811974c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R30f595e472b746f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R755ccdfd5ed94894"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rb6c1c770d0d7441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ra425b7d2772c4217"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R77d1e553d8034040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rc0be205dfe0e4479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rbbe5317dcc284ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re7cbd2e17e034fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R6229fca564f142d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R6b2adde982834a9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R01fc5a32222b4978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R3ffa2b2370f048ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Ra47b2682682a4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R9dd95d42746d4b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R5b9cdf48a53c4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rc9d5fb777fb44abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R14fa3ef838cc44aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R55f63838b3964f81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf359047c87034c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbc362e92d8664dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R04d851aeaf634335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfbe4b9bc52404cbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R05136f4f9e1e4ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rfbc64a45c48b45a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R643de24eea074a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rfbdaae0e21ef49e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rfde64f9a79b04d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R838b8e8b7b09431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rd93540d0585f41c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rbe22df2114bf4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re7ba93600950476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8db7bfa0c74b4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rc96834aaf3c942aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8b3fa128e4ce4496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra2edff38cac046c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1694899801eb4522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R521f8d1b602648a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R9f3194909d524053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R159488ce4dd14852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re98c395abb6747de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R5560281e43b54f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R8ad2b5c4a4e245f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R490685ef94764d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R868c5bf0e8da4a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R33e7c412e2a64345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R83ddaff2f8e24f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd7909882476e486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rfdc46dd1153c4a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R07e1f1279c9749da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R996675c4a08d4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R4610eb95c86545ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rce22e65cf91347af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>130</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
-        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Défini")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Établi")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$13,"P0")</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>130</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>20</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4234,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd00d0d947dfd4ec1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra61c6ef4bb3942a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4374,61 +4368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4480,8 +4474,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4872,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1cb0160e5c94b10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra26925b5e34f42cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5012,61 +5006,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5118,8 +5112,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5169,8 +5163,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5510,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e369f01065c4db9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116a71934f694304"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5650,61 +5644,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5756,8 +5750,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5807,8 +5801,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5858,8 +5852,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6148,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc130bd4ee77e4ec0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa9823eb42b4447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6288,61 +6282,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6394,8 +6388,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6447,8 +6441,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6500,8 +6494,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6606,8 +6600,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6659,8 +6653,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6712,8 +6706,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6765,8 +6759,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6818,8 +6812,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6871,8 +6865,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6908,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71116b2dac7145af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24dea8f4e054b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,61 +7042,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7154,8 +7148,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7205,8 +7199,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7256,8 +7250,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7307,8 +7301,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7358,8 +7352,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7409,8 +7403,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7460,8 +7454,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7511,8 +7505,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7546,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R764a50b2c6104cb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04e71cb5911e4218"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7686,61 +7680,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7786,10 +7780,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7825,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R628259cf60c84c7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3264dcf0bf0d46a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7965,61 +7959,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8065,10 +8059,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8114,10 +8108,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8153,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5cc54443cf84ade"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R329fabec68bd49c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8293,61 +8287,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8393,10 +8387,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8432,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9d0a0ed02d64d79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cc078d4a6654694"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8572,61 +8566,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8676,8 +8670,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8725,8 +8719,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8774,8 +8768,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8823,8 +8817,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8872,8 +8866,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8921,8 +8915,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8956,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ad6e5a522bf4764"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5571b175ca3d4e21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9096,61 +9090,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9196,10 +9190,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9245,10 +9239,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9294,10 +9288,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9333,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd517ffd2bb3c4b89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58549503b9b0485a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9473,61 +9467,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9579,8 +9573,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9630,8 +9624,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9681,8 +9675,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9732,8 +9726,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9767,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R341f27ea204344df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5df12a91b54230"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9907,61 +9901,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10013,8 +10007,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10064,8 +10058,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10115,8 +10109,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10166,8 +10160,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10217,8 +10211,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10268,8 +10262,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10319,8 +10313,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10370,8 +10364,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10421,8 +10415,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10472,8 +10466,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10507,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red2a009f9dd04cce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec1b506eb27a496c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10647,61 +10641,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10753,8 +10747,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10804,8 +10798,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10855,8 +10849,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10906,8 +10900,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10957,8 +10951,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11008,8 +11002,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11059,8 +11053,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11110,8 +11104,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11161,8 +11155,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11212,8 +11206,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11247,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7a6cc30007a4a67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e0d9762ae244cdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11387,61 +11381,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11493,8 +11487,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11544,8 +11538,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11595,8 +11589,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11646,8 +11640,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11681,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3107364702149f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55356b7bb24d4743"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11821,61 +11815,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11925,8 +11919,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11974,8 +11968,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12023,8 +12017,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12072,8 +12066,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12121,8 +12115,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12156,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5182d0cd96dd4b97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457d4185c07f4b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12296,61 +12290,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12400,8 +12394,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12449,8 +12443,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12498,8 +12492,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12547,8 +12541,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12596,8 +12590,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12645,8 +12639,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12694,8 +12688,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12743,8 +12737,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12778,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf72b4ab99e914458"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b594af936a4c94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12918,61 +12912,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13024,8 +13018,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13075,8 +13069,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13126,8 +13120,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13177,8 +13171,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13228,8 +13222,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13279,8 +13273,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13330,8 +13324,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13381,8 +13375,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13424,8 +13418,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13467,8 +13461,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13510,8 +13504,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13553,8 +13547,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13588,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788fa901558243b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f53ccd130a47e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13728,61 +13722,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13828,10 +13822,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Retribution</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13877,10 +13871,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13926,10 +13920,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13973,8 +13967,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14020,10 +14014,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>RET-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14067,8 +14061,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14114,10 +14108,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>RET-SRC-AND</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14153,7 +14147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f3686ec071a4b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07b31c5b37874517"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14218,10 +14212,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14265,12 +14259,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Grayson, Kahlee, Anderson, Kai Leng et réseaux d’Omega ; prototypes d’investigation, extraction et protection d’élèves.</x:v>
+        <x:v>158 fiches de production ; 5 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14289,11 +14283,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14446,22 +14440,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14670,13 +14664,13 @@
       <x:c r="F38" s="2"/>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+      <x:c r="A39" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="str">
+      <x:c r="B39" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
@@ -14753,10 +14747,16 @@
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
+    <x:row r="45" ht="96" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 5 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D45" s="2"/>
       <x:c r="E45" s="2"/>
       <x:c r="F45" s="2"/>
@@ -15312,6 +15312,14 @@
       <x:c r="D114" s="2"/>
       <x:c r="E114" s="2"/>
       <x:c r="F114" s="2"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="2"/>
+      <x:c r="B115" s="2"/>
+      <x:c r="C115" s="2"/>
+      <x:c r="D115" s="2"/>
+      <x:c r="E115" s="2"/>
+      <x:c r="F115" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15453,61 +15461,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15553,10 +15561,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15602,10 +15610,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15651,10 +15659,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RET-SRC-LIS</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Liselle</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15700,10 +15708,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>RET-SRC-OMEGA</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Omega</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15749,10 +15757,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>RET-SRC-SAN</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Sanak</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15798,10 +15806,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>RET-SRC-AND</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15847,10 +15855,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>RET-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15886,7 +15894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R158bc03217344d16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R702caafafa494c12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15913,7 +15921,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="91" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16026,65 +16034,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>RET-REF-CERBERUS</x:v>
       </x:c>
@@ -16092,7 +16100,7 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16111,7 +16119,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.ret.cerberus ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire RET-REF-CERBERUS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver le parcours de Grayson et les états nécessaires à Deception et ME3. Les rencontres proposées n’offrent ni guérison canonique de Grayson ni élimination définitive de Kai Leng.</x:v>
@@ -16126,14 +16134,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>RET-REF-REAPERS</x:v>
       </x:c>
@@ -16141,7 +16149,7 @@
         <x:v>Moissonneurs</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16160,7 +16168,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.ret.reapers ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire RET-REF-REAPERS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver le parcours de Grayson et les états nécessaires à Deception et ME3. Les rencontres proposées n’offrent ni guérison canonique de Grayson ni élimination définitive de Kai Leng.</x:v>
@@ -16175,14 +16183,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>RET-REF-TURIANS</x:v>
       </x:c>
@@ -16190,7 +16198,7 @@
         <x:v>Force d’intervention turienne</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16209,7 +16217,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Codex ref.ret.turians ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire RET-REF-TURIANS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Préserver le parcours de Grayson et les états nécessaires à Deception et ME3. Les rencontres proposées n’offrent ni guérison canonique de Grayson ni élimination définitive de Kai Leng.</x:v>
@@ -16224,11 +16232,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16263,7 +16271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9552afeab5fc49d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52acc7a18c964090"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16290,7 +16298,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16403,65 +16411,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>RET-REF-OMEGA</x:v>
       </x:c>
@@ -16469,7 +16477,7 @@
         <x:v>Omega</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16488,7 +16496,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.ret.omega ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire RET-REF-OMEGA consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver le parcours de Grayson et les états nécessaires à Deception et ME3. Les rencontres proposées n’offrent ni guérison canonique de Grayson ni élimination définitive de Kai Leng.</x:v>
@@ -16503,11 +16511,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -16552,14 +16560,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-AND</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>RET-REF-ACADEMY</x:v>
       </x:c>
@@ -16567,7 +16575,7 @@
         <x:v>Académie Grissom</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16586,7 +16594,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Codex ref.ret.academy ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire RET-REF-ACADEMY consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Préserver le parcours de Grayson et les états nécessaires à Deception et ME3. Les rencontres proposées n’offrent ni guérison canonique de Grayson ni élimination définitive de Kai Leng.</x:v>
@@ -16601,11 +16609,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16640,7 +16648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52d0588063d644ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref538463321f4481"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16780,61 +16788,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16884,8 +16892,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16935,8 +16943,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16986,8 +16994,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17037,8 +17045,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17088,8 +17096,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17139,8 +17147,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17190,8 +17198,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17241,8 +17249,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17278,7 +17286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc188f5299a4e4a82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2fd6ff7f16491f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17418,61 +17426,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17524,8 +17532,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17577,8 +17585,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17630,8 +17638,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17683,8 +17691,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17736,8 +17744,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17789,8 +17797,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17842,8 +17850,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17895,8 +17903,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17932,7 +17940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9f33a2b50aa40b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411952e6bd3a4f69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18072,61 +18080,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18178,8 +18186,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18229,8 +18237,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18280,8 +18288,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18331,8 +18339,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18382,8 +18390,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18433,8 +18441,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18484,8 +18492,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18535,8 +18543,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18570,7 +18578,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0ba15d3553e4879"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc544c90a17544aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18710,61 +18718,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18810,10 +18818,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>RET-SRC-KAI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Kai_Leng</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18859,10 +18867,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>RET-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200767/mass-effect-retribution-by-drew-karpyshyn/paperback/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18898,7 +18906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5532608ea64830"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67fd364f7064f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R643de24eea074a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rfbdaae0e21ef49e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rfde64f9a79b04d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R838b8e8b7b09431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rd93540d0585f41c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rbe22df2114bf4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re7ba93600950476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8db7bfa0c74b4f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rc96834aaf3c942aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8b3fa128e4ce4496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Ra2edff38cac046c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1694899801eb4522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R521f8d1b602648a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R9f3194909d524053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R159488ce4dd14852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re98c395abb6747de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R5560281e43b54f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R8ad2b5c4a4e245f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R490685ef94764d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R868c5bf0e8da4a61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R33e7c412e2a64345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R83ddaff2f8e24f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd7909882476e486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rfdc46dd1153c4a38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R07e1f1279c9749da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R996675c4a08d4461"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R4610eb95c86545ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rce22e65cf91347af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd56826bb84da447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R43a54dfcb7f74b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R01c58f7aa4d6438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R98610032e80242f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Reefe9925a7f744bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R04d9f2aea03144c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4845681942ba46e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R36902415cb044748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R0fcc0095e1ea48c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6e496dc8c8434996"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rdb4d3763522342e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R51dd4c43eb004a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rb24fd33f3c0d47da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R28c68124138a4164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfe248eaca0c34c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R089db5334482422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rec57f68c65d54a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R64f5cd9a140a4c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R259fa4dd2a1d40e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf793402a01164647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R87e97f4a32d942c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R27633366d60c449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R7e96fe1f108e41b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Refba8dc3fe7b40d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R89bc00332eda4f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0b8c24d730fb47fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R924218572d2242ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R5fe3688915514e61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra61c6ef4bb3942a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e5b79a1ed4b4e4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra26925b5e34f42cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74cf204f829643e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116a71934f694304"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a59818e5650476f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa9823eb42b4447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8461671a0eb4a24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24dea8f4e054b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6a6518b723a4d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04e71cb5911e4218"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779a969cf97d4f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3264dcf0bf0d46a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2073801f3a094980"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R329fabec68bd49c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd823ee01ad2b466c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cc078d4a6654694"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e8342777554b75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5571b175ca3d4e21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R810d2b42570a44b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58549503b9b0485a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R556bb52394d34067"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5df12a91b54230"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R290a549b89c44bd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec1b506eb27a496c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c6a2543f98f4bf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e0d9762ae244cdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce773019d68a4b29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55356b7bb24d4743"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bd6ce449e9148b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457d4185c07f4b7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R561dae121e584962"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b594af936a4c94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f11a2816d854574"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f53ccd130a47e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccba04ec25b54f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14147,7 +14147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07b31c5b37874517"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ddfed4b14294397"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15894,7 +15894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R702caafafa494c12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d0729b19da641f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16271,7 +16271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52acc7a18c964090"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R226c484d06534bf6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16648,7 +16648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref538463321f4481"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa099605362247cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17286,7 +17286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2fd6ff7f16491f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86cae89e30824203"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17940,7 +17940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411952e6bd3a4f69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32e3da6b1f2a49b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18578,7 +18578,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc544c90a17544aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b86713b827d4926"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18906,7 +18906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67fd364f7064f5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c971186211b4e27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd56826bb84da447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R43a54dfcb7f74b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R01c58f7aa4d6438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R98610032e80242f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Reefe9925a7f744bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R04d9f2aea03144c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4845681942ba46e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R36902415cb044748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R0fcc0095e1ea48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6e496dc8c8434996"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rdb4d3763522342e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R51dd4c43eb004a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rb24fd33f3c0d47da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R28c68124138a4164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfe248eaca0c34c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R089db5334482422e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rec57f68c65d54a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R64f5cd9a140a4c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R259fa4dd2a1d40e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf793402a01164647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R87e97f4a32d942c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R27633366d60c449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R7e96fe1f108e41b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Refba8dc3fe7b40d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R89bc00332eda4f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0b8c24d730fb47fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R924218572d2242ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R5fe3688915514e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rac101576ee704e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4989f26359c5412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R840aac8716874f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R51fcf7e397bc4410"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6cf4d4d61beb4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R18fe44d97d534b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R075c009ca8924372"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1aa0c747d8c24677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfe91d8a000d64302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb3d279551e664e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R038663d25d19465f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rff233626c31b4e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R245c1bbdc9ba477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R9f071e773a3b486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R265db2d4374d4308"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R6808d910f4784ebd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R6cac9d90f3f943e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R27a285cb00b04dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rd7644115a1b84892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R61f78c9dbd35494c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R2e19c029e4d74282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R2ba8f3a0e4214440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R160936de61c84888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R858e09099f07452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb559cbbb970345a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R454f3717699c4485"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Re760e1afc34b4236"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R56373fed71e04ff6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e5b79a1ed4b4e4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf68c3fee562443dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74cf204f829643e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2763173a30446a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a59818e5650476f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbac4de4aba584460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8461671a0eb4a24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88c1474674364aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6a6518b723a4d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf02e58e4774e47f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779a969cf97d4f3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7df6364cc23463c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2073801f3a094980"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1141ab08b0e84587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd823ee01ad2b466c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e6021a2dd1d4620"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e8342777554b75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e82138825154de1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R810d2b42570a44b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e2bd499c1574b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R556bb52394d34067"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93119cc2835e459b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R290a549b89c44bd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f52afc97cf434c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c6a2543f98f4bf1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra921f2b3535f43c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce773019d68a4b29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94fb9c0121054be8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bd6ce449e9148b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34ffe0d0895247cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R561dae121e584962"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34ffb0b7a01423d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f11a2816d854574"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dfde54f6a434b74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccba04ec25b54f3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ede32e183e44b8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14147,7 +14147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ddfed4b14294397"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c30146e00174974"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15894,7 +15894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d0729b19da641f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36080b6a0a24d92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16271,7 +16271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R226c484d06534bf6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b93478646a74eba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16648,7 +16648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa099605362247cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb9613015bb40a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17286,7 +17286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86cae89e30824203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec7bae448eb4233"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17940,7 +17940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32e3da6b1f2a49b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb59df38ce3a4c44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18578,7 +18578,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b86713b827d4926"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R463cb3846e9244a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18906,7 +18906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c971186211b4e27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477ae82037f24eca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Retribution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rac101576ee704e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4989f26359c5412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R840aac8716874f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R51fcf7e397bc4410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6cf4d4d61beb4796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R18fe44d97d534b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R075c009ca8924372"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1aa0c747d8c24677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfe91d8a000d64302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb3d279551e664e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R038663d25d19465f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rff233626c31b4e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R245c1bbdc9ba477d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R9f071e773a3b486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R265db2d4374d4308"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R6808d910f4784ebd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R6cac9d90f3f943e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R27a285cb00b04dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rd7644115a1b84892"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R61f78c9dbd35494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R2e19c029e4d74282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R2ba8f3a0e4214440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R160936de61c84888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R858e09099f07452d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb559cbbb970345a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R454f3717699c4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Re760e1afc34b4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R56373fed71e04ff6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7a1e6c8305cf48cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4850718c0abe4418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rf1e122c9327644c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R3ef0e410cd0c4a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R1757d533735844fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3537736c48ee484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R27b37d9f20104171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rbf0f30d861f542fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R6ec4956c80f24bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rc955dde7c3de4f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7a72c47e9133421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2eeea436847441a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rc4c54989b9db4ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc7672497dd3a413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R494a9161ffff44ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rb0d10f25dee2456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2b1fd5a0f48043ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R4d3b5aa74a3840a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R76c1090b7a5b4bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf9a4463efb0949a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rd1450193fcac4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R0e9c9adc43584028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf9eb118ed5514580"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R6d8d33d0a5e24d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R081deb1b748049b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R08c1b6a12a7549c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R007bd390acff4a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R15c9775be2a34c37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf68c3fee562443dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b59be9d6e3d41d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2763173a30446a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb4ddcf528f408f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbac4de4aba584460"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77135f7d9ad6443a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88c1474674364aac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d14a571cc54668"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf02e58e4774e47f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69ba5d3100bb4604"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7df6364cc23463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c92657e4284926"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1141ab08b0e84587"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re870af2717094c24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e6021a2dd1d4620"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07fb8c50fc724efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e82138825154de1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfee5fe9381274a75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e2bd499c1574b44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ca951dfe7f4f04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93119cc2835e459b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R563999199e7942b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f52afc97cf434c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R823465bd1c774928"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra921f2b3535f43c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3900cb3a81284138"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94fb9c0121054be8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aceddcaaeb74711"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34ffe0d0895247cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf236181cdef24c60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34ffb0b7a01423d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d79820ac6494b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dfde54f6a434b74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc814d77234c44252"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ede32e183e44b8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26f083af00ac4526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14147,7 +14147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c30146e00174974"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf502b3264c524e59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15894,7 +15894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36080b6a0a24d92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a7c100c11924126"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16271,7 +16271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b93478646a74eba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R810c8dc1b3a6453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16648,7 +16648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb9613015bb40a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf021460d76004e76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17286,7 +17286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec7bae448eb4233"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7248c8bb55154c2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17940,7 +17940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb59df38ce3a4c44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbfeda69bd8d4a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18578,7 +18578,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R463cb3846e9244a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1558f5defa45fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18906,7 +18906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477ae82037f24eca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5296e988a87242be"/>
   </x:tableParts>
 </x:worksheet>
 </file>